--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20211.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20211.xlsx
@@ -489,25 +489,25 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>77.27</v>
+        <v>90.91</v>
       </c>
       <c r="H2">
-        <v>22.73</v>
+        <v>9.09</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>22.73</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -594,25 +594,25 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>63.64</v>
+        <v>86.36</v>
       </c>
       <c r="H5">
-        <v>36.36</v>
+        <v>13.64</v>
       </c>
       <c r="I5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>36.36</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -678,22 +678,25 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>9.09</v>
+      </c>
+      <c r="I2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -710,22 +713,25 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>24.24</v>
+      </c>
+      <c r="I3">
+        <v>8.1</v>
       </c>
       <c r="J3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -742,22 +748,25 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>30.3</v>
+      </c>
+      <c r="I4">
+        <v>7.7</v>
       </c>
       <c r="J4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -774,22 +783,25 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>27.27</v>
+      </c>
+      <c r="I5">
+        <v>7.2</v>
       </c>
       <c r="J5">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
   </sheetData>
@@ -855,25 +867,25 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>77.27</v>
+        <v>90.91</v>
       </c>
       <c r="H2">
-        <v>22.73</v>
+        <v>9.09</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>22.73</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -890,19 +902,19 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>60.61</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H3">
-        <v>39.39</v>
+        <v>24.24</v>
       </c>
       <c r="I3">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -925,19 +937,19 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>57.58</v>
+        <v>69.7</v>
       </c>
       <c r="H4">
-        <v>42.42</v>
+        <v>30.3</v>
       </c>
       <c r="I4">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -960,25 +972,25 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>63.64</v>
+        <v>86.36</v>
       </c>
       <c r="H5">
-        <v>36.36</v>
+        <v>13.64</v>
       </c>
       <c r="I5">
         <v>6.6</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>36.36</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20211.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,6 +82,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -134,8 +138,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -436,42 +442,45 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -494,19 +503,19 @@
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>90.91</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>9.09</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J2">
         <v>2</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>9.09</v>
       </c>
     </row>
@@ -529,19 +538,19 @@
       <c r="F3">
         <v>13</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>60.61</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>39.39</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>5.8</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -564,19 +573,19 @@
       <c r="F4">
         <v>14</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>57.58</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>42.42</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>6.4</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -599,19 +608,19 @@
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>86.36</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>13.64</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>6.2</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -625,42 +634,45 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -683,19 +695,19 @@
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>90.91</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>9.09</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J2">
         <v>2</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>9.09</v>
       </c>
     </row>
@@ -718,19 +730,19 @@
       <c r="F3">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>75.76000000000001</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>24.24</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -753,19 +765,19 @@
       <c r="F4">
         <v>10</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>69.7</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>30.3</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7.7</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -788,19 +800,19 @@
       <c r="F5">
         <v>6</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>72.73</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>27.27</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.2</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>22.73</v>
       </c>
     </row>
@@ -814,42 +826,45 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -872,19 +887,19 @@
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>90.91</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>9.09</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8.6</v>
       </c>
       <c r="J2">
         <v>2</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>9.09</v>
       </c>
     </row>
@@ -907,19 +922,19 @@
       <c r="F3">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>75.76000000000001</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>24.24</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>6.9</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -942,19 +957,19 @@
       <c r="F4">
         <v>10</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>69.7</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>30.3</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -977,19 +992,19 @@
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>86.36</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>13.64</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>6.6</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20211.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20211.xlsx
@@ -83,7 +83,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20211.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20211.xlsx
@@ -498,25 +498,25 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>90.91</v>
+        <v>95.45</v>
       </c>
       <c r="H2" s="1">
-        <v>9.09</v>
+        <v>4.55</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -690,25 +690,25 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>90.91</v>
+        <v>95.45</v>
       </c>
       <c r="H2" s="1">
-        <v>9.09</v>
+        <v>4.55</v>
       </c>
       <c r="I2" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -795,25 +795,25 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>72.73</v>
+        <v>90.91</v>
       </c>
       <c r="H5" s="1">
-        <v>27.27</v>
+        <v>9.09</v>
       </c>
       <c r="I5" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -894,13 +894,13 @@
         <v>9.09</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -917,19 +917,19 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>75.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>24.24</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -952,19 +952,19 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>69.7</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -987,19 +987,19 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>86.36</v>
+        <v>95.45</v>
       </c>
       <c r="H5" s="1">
-        <v>13.64</v>
+        <v>4.55</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
         <v>0</v>
